--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -565,9 +565,11 @@
         <v>34.28</v>
       </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>3.69</v>
+      </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="4">
@@ -685,9 +687,11 @@
         <v>55.3</v>
       </c>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>3.46</v>
+      </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="7">

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,7 +522,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>158.01</v>
+        <v>157.65</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -562,14 +562,14 @@
         <v>99.18000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>34.28</v>
+        <v>34.06</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>3.69</v>
+        <v>3.02</v>
       </c>
       <c r="L3" t="n">
-        <v>3.66</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -604,7 +604,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>6.17</v>
+        <v>6.34</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -644,7 +644,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>14.8</v>
+        <v>15.34</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -684,14 +684,14 @@
         <v>53.45</v>
       </c>
       <c r="I6" t="n">
-        <v>55.3</v>
+        <v>54.65</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>3.46</v>
+        <v>2.25</v>
       </c>
       <c r="L6" t="n">
-        <v>1.85</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="7">
@@ -726,7 +726,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>267.25</v>
+        <v>266.39</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -766,7 +766,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>53.6</v>
+        <v>52.5</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -806,11 +806,411 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>6.2</v>
+        <v>6.34</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PSX</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>264.94</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-883.4</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>290.55</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CVX</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>247.32</v>
+      </c>
+      <c r="D11" t="n">
+        <v>205.58</v>
+      </c>
+      <c r="E11" t="n">
+        <v>414.28</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>224.37</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RGA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>257.81</v>
+      </c>
+      <c r="D12" t="n">
+        <v>246.97</v>
+      </c>
+      <c r="E12" t="n">
+        <v>293.58</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>266.8</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DHT</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>375.99</v>
+      </c>
+      <c r="D13" t="n">
+        <v>21.83</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1934.29</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>23.03</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DDOG</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>247.67</v>
+      </c>
+      <c r="D14" t="n">
+        <v>245.19</v>
+      </c>
+      <c r="E14" t="n">
+        <v>256.35</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>260.36</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MPC</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>67</v>
+      </c>
+      <c r="D15" t="n">
+        <v>425.18</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-1329.9</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>473.69</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>HALO</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>201.26</v>
+      </c>
+      <c r="D16" t="n">
+        <v>110.58</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1080.86</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CLMT</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>98.54000000000001</v>
+      </c>
+      <c r="D17" t="n">
+        <v>53.45</v>
+      </c>
+      <c r="E17" t="n">
+        <v>265.37</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>55.54</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>RBRK</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="D18" t="n">
+        <v>106.39</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-442.58</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>113.41</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>HZO</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>39.94</v>
+      </c>
+      <c r="D19" t="n">
+        <v>50.81</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>52.01</v>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="n">
         <v>0</v>
       </c>
     </row>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,7 +522,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>157.65</v>
+        <v>157.91</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -562,14 +562,14 @@
         <v>99.18000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>34.06</v>
+        <v>34.25</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>3.02</v>
+        <v>3.6</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="4">
@@ -604,7 +604,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>6.34</v>
+        <v>6.31</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -644,7 +644,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>15.34</v>
+        <v>15.21</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -684,14 +684,14 @@
         <v>53.45</v>
       </c>
       <c r="I6" t="n">
-        <v>54.65</v>
+        <v>54.52</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="7">
@@ -726,7 +726,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>266.39</v>
+        <v>272.32</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -766,7 +766,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>52.5</v>
+        <v>52.07</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -806,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>6.34</v>
+        <v>6.24</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -846,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>290.55</v>
+        <v>291.03</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>224.37</v>
+        <v>225.71</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -926,7 +926,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>266.8</v>
+        <v>267.39</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -966,7 +966,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>23.03</v>
+        <v>23.35</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>260.36</v>
+        <v>256.43</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
@@ -1046,7 +1046,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>473.69</v>
+        <v>475.04</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -1086,7 +1086,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>122.5</v>
+        <v>124.37</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -1126,7 +1126,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>55.54</v>
+        <v>56.05</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -1166,7 +1166,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>113.41</v>
+        <v>114.59</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -1206,11 +1206,451 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>52.01</v>
+        <v>52.36</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>GTE</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="E20" t="n">
+        <v>34.26</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>11.31</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>GIC</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>40.08</v>
+      </c>
+      <c r="D21" t="n">
+        <v>41.95</v>
+      </c>
+      <c r="E21" t="n">
+        <v>32.97</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>44.12</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SM</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>270.61</v>
+      </c>
+      <c r="D22" t="n">
+        <v>35.91</v>
+      </c>
+      <c r="E22" t="n">
+        <v>998.1799999999999</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>38.85</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PMTS</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>26.47</v>
+      </c>
+      <c r="D23" t="n">
+        <v>26.21</v>
+      </c>
+      <c r="E23" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" t="n">
+        <v>79.41</v>
+      </c>
+      <c r="I23" t="n">
+        <v>27.04</v>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CNQ</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>233.62</v>
+      </c>
+      <c r="D24" t="n">
+        <v>49.08</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1119.41</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>54.18</v>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MEOH</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>115.7</v>
+      </c>
+      <c r="D25" t="n">
+        <v>59.61</v>
+      </c>
+      <c r="E25" t="n">
+        <v>283.97</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>63.31</v>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>WST</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>360.29</v>
+      </c>
+      <c r="D26" t="n">
+        <v>357.69</v>
+      </c>
+      <c r="E26" t="n">
+        <v>370.17</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>388.78</v>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SLDE</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>56.03</v>
+      </c>
+      <c r="D27" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="E27" t="n">
+        <v>214.03</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>27.34</v>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>JOE</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>67</v>
+      </c>
+      <c r="D28" t="n">
+        <v>65.73</v>
+      </c>
+      <c r="E28" t="n">
+        <v>70.81</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>67</v>
+      </c>
+      <c r="I28" t="n">
+        <v>68.98999999999999</v>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ZETA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>171.94</v>
+      </c>
+      <c r="D29" t="n">
+        <v>30.66</v>
+      </c>
+      <c r="E29" t="n">
+        <v>864.21</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>33.55</v>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ELF</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>74.98999999999999</v>
+      </c>
+      <c r="D30" t="n">
+        <v>103.01</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-17.48</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>114.74</v>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="n">
         <v>0</v>
       </c>
     </row>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,7 +522,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>157.91</v>
+        <v>157.88</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -562,14 +562,14 @@
         <v>99.18000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>34.25</v>
+        <v>33.97</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="L3" t="n">
-        <v>3.57</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="4">
@@ -604,7 +604,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>6.31</v>
+        <v>6.26</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -644,7 +644,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>15.21</v>
+        <v>15.62</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -684,14 +684,14 @@
         <v>53.45</v>
       </c>
       <c r="I6" t="n">
-        <v>54.52</v>
+        <v>55.69</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>4.19</v>
       </c>
       <c r="L6" t="n">
-        <v>1.07</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="7">
@@ -726,7 +726,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>272.32</v>
+        <v>269.13</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -766,7 +766,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>52.07</v>
+        <v>52.4</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -806,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>6.24</v>
+        <v>6.25</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -846,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>291.03</v>
+        <v>290.07</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>225.71</v>
+        <v>226.78</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -926,7 +926,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>267.39</v>
+        <v>269.18</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -966,7 +966,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>23.35</v>
+        <v>24.16</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>256.43</v>
+        <v>273.09</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
@@ -1046,7 +1046,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>475.04</v>
+        <v>467.98</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -1086,7 +1086,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>124.37</v>
+        <v>124.83</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -1126,7 +1126,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>56.05</v>
+        <v>52.59</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -1166,7 +1166,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>114.59</v>
+        <v>120.38</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -1206,7 +1206,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>52.36</v>
+        <v>52.42</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -1246,7 +1246,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>11.31</v>
+        <v>11.58</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -1286,7 +1286,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>44.12</v>
+        <v>44.88</v>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -1326,7 +1326,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>38.85</v>
+        <v>38.61</v>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>WIN</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1366,12 +1366,16 @@
         <v>79.41</v>
       </c>
       <c r="I23" t="n">
-        <v>27.04</v>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+        <v>27.55</v>
+      </c>
+      <c r="J23" t="n">
+        <v>27.55</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.08</v>
+      </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="24">
@@ -1406,7 +1410,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>54.18</v>
+        <v>54.24</v>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -1446,7 +1450,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>63.31</v>
+        <v>63.14</v>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
@@ -1486,7 +1490,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>388.78</v>
+        <v>393.48</v>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
@@ -1526,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>27.34</v>
+        <v>27.11</v>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
@@ -1566,12 +1570,14 @@
         <v>67</v>
       </c>
       <c r="I28" t="n">
-        <v>68.98999999999999</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="n">
+        <v>2.13</v>
+      </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="29">
@@ -1606,7 +1612,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>33.55</v>
+        <v>34.11</v>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
@@ -1646,11 +1652,251 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>114.74</v>
+        <v>113.78</v>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>270.61</v>
+      </c>
+      <c r="D31" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1002.88</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>78.22</v>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>WSM</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>233.62</v>
+      </c>
+      <c r="D32" t="n">
+        <v>232.95</v>
+      </c>
+      <c r="E32" t="n">
+        <v>236.17</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>253.32</v>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AMG</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>375.99</v>
+      </c>
+      <c r="D33" t="n">
+        <v>367.86</v>
+      </c>
+      <c r="E33" t="n">
+        <v>412.57</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>393.66</v>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>REPX</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>257.81</v>
+      </c>
+      <c r="D34" t="n">
+        <v>43.59</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2400.01</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>48.34</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>NSIT</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>56.58</v>
+      </c>
+      <c r="D35" t="n">
+        <v>156.2</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-361.82</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>171.19</v>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>NOG</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>242.68</v>
+      </c>
+      <c r="D36" t="n">
+        <v>24.78</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1223.23</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>27.44</v>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="n">
         <v>0</v>
       </c>
     </row>

--- a/trading_journal.xlsx
+++ b/trading_journal.xlsx
@@ -562,7 +562,7 @@
         <v>91.8</v>
       </c>
       <c r="I3" t="n">
-        <v>16.87</v>
+        <v>16.86</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -602,7 +602,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>50.86</v>
+        <v>50.97</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -642,7 +642,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>236.83</v>
+        <v>237.11</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -682,7 +682,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>232.73</v>
+        <v>233.12</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -722,7 +722,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>11.44</v>
+        <v>11.23</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -762,7 +762,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>40.02</v>
+        <v>40.14</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -802,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>33.38</v>
+        <v>33.49</v>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>251.51</v>
+        <v>251.24</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -882,7 +882,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>67.88</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -922,7 +922,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>76.15000000000001</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -962,7 +962,7 @@
         <v>23</v>
       </c>
       <c r="I13" t="n">
-        <v>111.78</v>
+        <v>111.71</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -1002,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>52.18</v>
+        <v>52.29</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
